--- a/output/graficos_dimensiones/comunal_i_ingr_a_2018_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2018_los lagos.xlsx
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:07</t>
+    <t xml:space="preserve">2026-09-09 23:00</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2018_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2018_los lagos.xlsx
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:00</t>
+    <t xml:space="preserve">2026-09-17 13:58</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2018_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2018_los lagos.xlsx
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 13:58</t>
+    <t xml:space="preserve">2026-09-23 12:27</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2018_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2018_los lagos.xlsx
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:27</t>
+    <t xml:space="preserve">2026-10-02 13:18</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2018_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2018_los lagos.xlsx
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:18</t>
+    <t xml:space="preserve">2026-10-05 09:57</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -571,7 +571,7 @@
         <v>2018</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>934418.62</v>
+        <v>934418.63</v>
       </c>
     </row>
     <row r="3">
@@ -656,7 +656,7 @@
         <v>2018</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>714893.12</v>
+        <v>714893.13</v>
       </c>
     </row>
     <row r="8">
@@ -758,7 +758,7 @@
         <v>2018</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>657624.12</v>
+        <v>657624.13</v>
       </c>
     </row>
     <row r="14">
@@ -826,7 +826,7 @@
         <v>2018</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>622815.12</v>
+        <v>622815.13</v>
       </c>
     </row>
     <row r="18">
@@ -877,7 +877,7 @@
         <v>2018</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>610401.62</v>
+        <v>610401.63</v>
       </c>
     </row>
     <row r="21">
@@ -945,7 +945,7 @@
         <v>2018</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>582440.12</v>
+        <v>582440.13</v>
       </c>
     </row>
     <row r="25">
